--- a/data/trans_orig/P1411-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2012</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23710</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,82 +746,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9710</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4416</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17394</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>24640</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>15355</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>35815</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9710</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4348</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17323</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>24640</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>16087</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>38469</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679759</t>
+          <t>678464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>695739</t>
+          <t>695658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,82 +859,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>687340</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>679656</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>692634</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1375879</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1364704</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1385164</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>687340</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>679727</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>692702</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1375879</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1362050</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1384432</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33283</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>46729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984664</t>
+          <t>985851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003817</t>
+          <t>1005510</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1010713</t>
+          <t>1009345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1023289</t>
+          <t>1023310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1999751</t>
+          <t>1999009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2023813</t>
+          <t>2024022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18732</t>
+          <t>17465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738891</t>
+          <t>740158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752407</t>
+          <t>752518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760687</t>
+          <t>761784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773716</t>
+          <t>773840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505989</t>
+          <t>1505949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523321</t>
+          <t>1523742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>24205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48797</t>
+          <t>47917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912666</t>
+          <t>911849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932606</t>
+          <t>932539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1032124</t>
+          <t>1032194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1046081</t>
+          <t>1045969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950843</t>
+          <t>1951723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975591</t>
+          <t>1975435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55533</t>
+          <t>54956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>92074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>52273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132212</t>
+          <t>132501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3334078</t>
+          <t>3334705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3371246</t>
+          <t>3371823</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3502303</t>
+          <t>3501643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3527271</t>
+          <t>3526754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6848482</t>
+          <t>6848193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6890882</t>
+          <t>6892418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2016</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649252</t>
+          <t>649432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665557</t>
+          <t>665847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653882</t>
+          <t>653479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667792</t>
+          <t>667242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1310033</t>
+          <t>1310692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1329537</t>
+          <t>1331038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29320</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>27090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48605</t>
+          <t>49987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>993111</t>
+          <t>994051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011312</t>
+          <t>1012451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1015400</t>
+          <t>1015823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1033449</t>
+          <t>1033155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2016739</t>
+          <t>2015357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2041127</t>
+          <t>2041812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739453</t>
+          <t>739709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753747</t>
+          <t>753772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>770214</t>
+          <t>771168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782632</t>
+          <t>781874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1514905</t>
+          <t>1516308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1533671</t>
+          <t>1533546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44691</t>
+          <t>44839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903421</t>
+          <t>903395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923430</t>
+          <t>923635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025266</t>
+          <t>1024607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1039002</t>
+          <t>1038744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1936655</t>
+          <t>1936507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1960057</t>
+          <t>1958948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51860</t>
+          <t>52334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>84642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60519</t>
+          <t>60112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92504</t>
+          <t>92978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136450</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3309125</t>
+          <t>3309708</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3342490</t>
+          <t>3342016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3484023</t>
+          <t>3484430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511710</t>
+          <t>3511946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6802442</t>
+          <t>6804640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6846388</t>
+          <t>6845914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1411-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>25277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>36897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678464</t>
+          <t>678192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>695658</t>
+          <t>695885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>679656</t>
+          <t>679915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>692634</t>
+          <t>692597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1364704</t>
+          <t>1363622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1385164</t>
+          <t>1384353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>33888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46729</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>985851</t>
+          <t>984059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005510</t>
+          <t>1004783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1009345</t>
+          <t>1009492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1023310</t>
+          <t>1023488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1999009</t>
+          <t>2000593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2024022</t>
+          <t>2024039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>17731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28848</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740158</t>
+          <t>739892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>752467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>761784</t>
+          <t>761539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773840</t>
+          <t>773773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505949</t>
+          <t>1506155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523742</t>
+          <t>1523362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24205</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47917</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911849</t>
+          <t>912844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932539</t>
+          <t>933525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1032194</t>
+          <t>1032656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1045969</t>
+          <t>1045906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951723</t>
+          <t>1951724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975435</t>
+          <t>1975312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54956</t>
+          <t>55594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>91189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52273</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88276</t>
+          <t>87559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132501</t>
+          <t>131258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3334705</t>
+          <t>3335590</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3371823</t>
+          <t>3371185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3501643</t>
+          <t>3502501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3526754</t>
+          <t>3526995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6848193</t>
+          <t>6849436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6892418</t>
+          <t>6893135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>37465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649432</t>
+          <t>650264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665847</t>
+          <t>665511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653479</t>
+          <t>653476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667242</t>
+          <t>667496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1310692</t>
+          <t>1310174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1331038</t>
+          <t>1329936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>28310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49987</t>
+          <t>47740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994051</t>
+          <t>994121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012451</t>
+          <t>1011045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1015823</t>
+          <t>1015253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1033155</t>
+          <t>1033412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2015357</t>
+          <t>2017604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2041812</t>
+          <t>2042129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739709</t>
+          <t>739742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753772</t>
+          <t>753842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>771168</t>
+          <t>770542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781874</t>
+          <t>782515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1516308</t>
+          <t>1515062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1533546</t>
+          <t>1534235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>43510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903395</t>
+          <t>904550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923635</t>
+          <t>923422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1024607</t>
+          <t>1024832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1038744</t>
+          <t>1039043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1936507</t>
+          <t>1937836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1958948</t>
+          <t>1959453</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52334</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84642</t>
+          <t>84785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60112</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>90718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>133851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3309708</t>
+          <t>3309565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3342016</t>
+          <t>3343114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3484430</t>
+          <t>3483550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511946</t>
+          <t>3511959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6804640</t>
+          <t>6805041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6845914</t>
+          <t>6848174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
